--- a/diseases/d032/2010-2014.xlsx
+++ b/diseases/d032/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2297,9 +2288,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2433,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3137,9 +3122,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -3285,9 +3267,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3977,9 +3956,6 @@
       <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -4125,9 +4101,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4817,9 +4790,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -4965,9 +4935,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -5657,9 +5624,6 @@
       <c r="O31" t="n">
         <v>5</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.01025234454459675</v>
       </c>
@@ -5805,9 +5769,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6497,9 +6458,6 @@
       <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01025234454459675</v>
       </c>
@@ -6645,9 +6603,6 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -7337,9 +7292,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -7485,9 +7437,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8177,9 +8126,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -8325,9 +8271,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9017,9 +8960,6 @@
       <c r="O51" t="n">
         <v>4</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -9165,9 +9105,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9857,9 +9794,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -10005,9 +9939,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10697,9 +10628,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10845,9 +10773,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11537,9 +11462,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11933,9 +11855,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12081,9 +12000,6 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -12773,9 +12689,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -12921,9 +12834,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13613,9 +13523,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -13761,9 +13668,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14453,9 +14357,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -14601,9 +14502,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15293,9 +15191,6 @@
       <c r="O88" t="n">
         <v>9</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01831962487677635</v>
       </c>
@@ -15441,9 +15336,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -16133,9 +16025,6 @@
       <c r="O93" t="n">
         <v>2</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -16281,9 +16170,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16973,9 +16859,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17121,9 +17004,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17961,9 +17841,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -18109,9 +17986,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18801,9 +18675,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -18949,9 +18820,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19641,9 +19509,6 @@
       <c r="O114" t="n">
         <v>2</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -19789,9 +19654,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20481,9 +20343,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20629,9 +20488,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21321,9 +21177,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -21469,9 +21322,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22161,9 +22011,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22557,9 +22404,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -22705,9 +22549,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23397,9 +23238,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -23545,9 +23383,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -24237,9 +24072,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -24385,9 +24217,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -25077,9 +24906,6 @@
       <c r="O146" t="n">
         <v>3</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.00604843837436162</v>
       </c>
@@ -25225,9 +25051,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -25917,9 +25740,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -26065,9 +25885,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -26757,9 +26574,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -26905,9 +26719,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -27597,9 +27408,6 @@
       <c r="O161" t="n">
         <v>5</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.01008073062393603</v>
       </c>
@@ -27745,9 +27553,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -28437,9 +28242,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28585,9 +28387,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -29277,9 +29076,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -29425,9 +29221,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -30561,9 +30354,6 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -30709,9 +30499,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -31993,9 +31780,6 @@
       <c r="O188" t="n">
         <v>2</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -32141,9 +31925,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33573,9 +33354,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -33721,9 +33499,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -35153,9 +34928,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -35549,9 +35321,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -35697,9 +35466,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -37129,9 +36895,6 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -37277,9 +37040,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -38561,9 +38321,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -38709,9 +38466,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -39993,9 +39747,6 @@
       <c r="O238" t="n">
         <v>3</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -40141,9 +39892,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -41425,9 +41173,6 @@
       <c r="O247" t="n">
         <v>2</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -41573,9 +41318,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -43005,9 +42747,6 @@
       <c r="O257" t="n">
         <v>1</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -43153,9 +42892,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -44437,9 +44173,6 @@
       <c r="O266" t="n">
         <v>3</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -44585,9 +44318,6 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -45869,9 +45599,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -46017,9 +45744,6 @@
       <c r="O276" t="n">
         <v>1</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -47449,9 +47173,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -47597,9 +47318,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -48881,9 +48599,6 @@
       <c r="O294" t="n">
         <v>2</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -49029,9 +48744,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -50461,9 +50173,6 @@
       <c r="O304" t="n">
         <v>2</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -50609,9 +50318,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -51893,9 +51599,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -52041,9 +51744,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -53473,9 +53173,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -53869,9 +53566,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -54017,9 +53711,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -55449,9 +55140,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -55597,9 +55285,6 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
@@ -56881,9 +56566,6 @@
       <c r="O344" t="n">
         <v>1</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -57029,9 +56711,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -58313,9 +57992,6 @@
       <c r="O353" t="n">
         <v>1</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -58461,9 +58137,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -59745,9 +59418,6 @@
       <c r="O362" t="n">
         <v>1</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -59893,9 +59563,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -61325,9 +60992,6 @@
       <c r="O372" t="n">
         <v>1</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -61473,9 +61137,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -62757,9 +62418,6 @@
       <c r="O381" t="n">
         <v>1</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -62905,9 +62563,6 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0</v>
       </c>
@@ -64337,9 +63992,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -64485,9 +64137,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -65769,9 +65418,6 @@
       <c r="O400" t="n">
         <v>1</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -65917,9 +65563,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -67201,9 +66844,6 @@
       <c r="O409" t="n">
         <v>0</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0</v>
       </c>
@@ -67349,9 +66989,6 @@
       <c r="O410" t="n">
         <v>2</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -68781,9 +68418,6 @@
       <c r="O419" t="n">
         <v>1</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -68929,9 +68563,6 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
@@ -70213,9 +69844,6 @@
       <c r="O428" t="n">
         <v>1</v>
       </c>
-      <c r="Q428" t="n">
-        <v>0</v>
-      </c>
       <c r="R428" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -70359,9 +69987,6 @@
         <v>0</v>
       </c>
       <c r="O429" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q429" t="n">
         <v>0</v>
       </c>
       <c r="R429" t="n">
